--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487003_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487003_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4845</v>
+        <v>4.7446</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2986</v>
+        <v>1.9659</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1859</v>
+        <v>2.7787</v>
       </c>
       <c r="G2" t="n">
         <v>4.9085</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0072</v>
+        <v>0.2674</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2085</v>
+        <v>-0.1242</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2013</v>
+        <v>0.3916</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0472</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.716</v>
+        <v>4.7192</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7689</v>
+        <v>3.4163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.3029</v>
       </c>
       <c r="G3" t="n">
         <v>4.4686</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2085</v>
+        <v>-0.2053</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3408</v>
+        <v>-0.0118</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5493</v>
+        <v>-0.1936</v>
       </c>
       <c r="V3" t="n">
         <v>-2.0082</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0547</v>
+        <v>4.3558</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9438</v>
+        <v>1.8645</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1109</v>
+        <v>2.4913</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4561</v>
+        <v>3.9957</v>
       </c>
       <c r="H4" t="n">
-        <v>1.943</v>
+        <v>0.9438</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5131</v>
+        <v>3.0519</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6684</v>
+        <v>2.2869</v>
       </c>
       <c r="K4" t="n">
-        <v>2.55</v>
+        <v>0.6297</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1184</v>
+        <v>1.6572</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7876</v>
+        <v>1.7087</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6071</v>
+        <v>0.314</v>
       </c>
       <c r="O4" t="n">
         <v>1.3947</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8214</v>
+        <v>2.0534</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8214</v>
+        <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2578</v>
+        <v>-0.1656</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7246</v>
+        <v>-0.6627</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.4971</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4805</v>
+        <v>-1.5277</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4805</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4935</v>
+        <v>3.8852</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2097</v>
+        <v>2.2189</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2838</v>
+        <v>1.6663</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9957</v>
+        <v>3.4561</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9438</v>
+        <v>1.943</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0519</v>
+        <v>1.5131</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2869</v>
+        <v>2.6684</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6297</v>
+        <v>2.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6572</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7087</v>
+        <v>0.7876</v>
       </c>
       <c r="N5" t="n">
-        <v>0.314</v>
+        <v>-0.6071</v>
       </c>
       <c r="O5" t="n">
         <v>1.3947</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0279</v>
+        <v>0.0882</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3174</v>
+        <v>-0.4495</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2896</v>
+        <v>0.5377</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5277</v>
+        <v>-0.4805</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7679</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8195</v>
+        <v>2.901</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.7443</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7342</v>
+        <v>3.6453</v>
       </c>
       <c r="G6" t="n">
         <v>0.1507</v>
@@ -922,13 +922,13 @@
         <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2142</v>
+        <v>-0.1327</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.5155</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4718</v>
+        <v>0.3828</v>
       </c>
       <c r="V6" t="n">
         <v>0.8295</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.697</v>
+        <v>-0.9442</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9356</v>
+        <v>-0.9264</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2386</v>
+        <v>-0.0177</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8815</v>
+        <v>1.5168</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1236</v>
+        <v>0.9436</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7579</v>
+        <v>0.5732</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2768</v>
+        <v>0.4211</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0389</v>
+        <v>1.3821</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3158</v>
+        <v>-0.9609</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3953</v>
+        <v>1.0957</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1626</v>
+        <v>-0.4385</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5579</v>
+        <v>1.5342</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7739</v>
+        <v>-0.2905</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6587</v>
+        <v>-0.713</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4326</v>
+        <v>0.4225</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5893</v>
+        <v>-0.9384</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5893</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7594</v>
+        <v>-1.2083</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2674</v>
+        <v>-1.7651</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.492</v>
+        <v>0.5568</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5168</v>
+        <v>-0.8815</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9436</v>
+        <v>-0.1236</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5732</v>
+        <v>-0.7579</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4211</v>
+        <v>-1.2768</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3821</v>
+        <v>0.0389</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9609</v>
+        <v>-1.3158</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0957</v>
+        <v>0.3953</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4385</v>
+        <v>-0.1626</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5342</v>
+        <v>0.5579</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1058</v>
+        <v>0.2626</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.054</v>
+        <v>-0.4882</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0518</v>
+        <v>0.7508</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9384</v>
+        <v>-0.5893</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3573</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8249</v>
+        <v>-1.7169</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0201</v>
+        <v>-4.4971</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1951</v>
+        <v>2.7801</v>
       </c>
       <c r="G9" t="n">
         <v>1.5859</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1254</v>
+        <v>-0.0174</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.1357</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5333</v>
+        <v>0.1183</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8619</v>
+        <v>-4.6527</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5847</v>
+        <v>-5.3755</v>
       </c>
       <c r="F10" t="n">
         <v>0.7229</v>
@@ -1234,10 +1234,10 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4997</v>
+        <v>-0.2905</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4611</v>
+        <v>-0.2519</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0386</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11.425</v>
+        <v>12.0837</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5016</v>
+        <v>-3.8428</v>
       </c>
       <c r="F11" t="n">
-        <v>15.9265</v>
+        <v>15.9266</v>
       </c>
       <c r="G11" t="n">
         <v>19.116</v>
       </c>
       <c r="H11" t="n">
-        <v>8.092399999999998</v>
+        <v>8.092400000000001</v>
       </c>
       <c r="I11" t="n">
         <v>11.0236</v>
@@ -1291,7 +1291,7 @@
         <v>10.6761</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8311999999999993</v>
+        <v>-0.8312000000000002</v>
       </c>
       <c r="M11" t="n">
         <v>9.271100000000001</v>
@@ -1312,13 +1312,13 @@
         <v>13.3472</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1426</v>
+        <v>-0.4838</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.0112</v>
+        <v>-3.3525</v>
       </c>
       <c r="U11" t="n">
-        <v>2.8687</v>
+        <v>2.868599999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-5.521599999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9668</v>
+        <v>2.4604</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2676</v>
+        <v>1.117</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6992</v>
+        <v>1.3435</v>
       </c>
       <c r="G12" t="n">
         <v>-2.079</v>
@@ -1390,13 +1390,13 @@
         <v>2.2588</v>
       </c>
       <c r="S12" t="n">
-        <v>2.44</v>
+        <v>0.9337</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2162</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2238</v>
+        <v>0.8681</v>
       </c>
       <c r="V12" t="n">
         <v>3.6057</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6377</v>
+        <v>0.7893</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5593</v>
+        <v>-1.1409</v>
       </c>
       <c r="F13" t="n">
-        <v>2.197</v>
+        <v>1.9302</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0792</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2097</v>
+        <v>0.3613</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5928</v>
+        <v>-0.1744</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8025</v>
+        <v>0.5357</v>
       </c>
       <c r="V13" t="n">
         <v>0.0698</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3481</v>
+        <v>0.5556</v>
       </c>
       <c r="E14" t="n">
         <v>-0.2969</v>
       </c>
       <c r="F14" t="n">
-        <v>0.645</v>
+        <v>0.8525</v>
       </c>
       <c r="G14" t="n">
         <v>-3.5853</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.315</v>
+        <v>-0.1075</v>
       </c>
       <c r="T14" t="n">
         <v>-0.6201</v>
       </c>
       <c r="U14" t="n">
-        <v>0.305</v>
+        <v>0.5125</v>
       </c>
       <c r="V14" t="n">
         <v>3.0164</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>F. ADEBAYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5239</v>
+        <v>-0.026</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6089</v>
+        <v>-0.2415</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.2155</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5525</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3763</v>
+        <v>1.3046</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9288</v>
+        <v>-1.3917</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.016</v>
+        <v>1.0167</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6813</v>
+        <v>2.4114</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6974</v>
+        <v>-1.3947</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5365</v>
+        <v>-1.1037</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.305</v>
+        <v>-1.1068</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2314</v>
+        <v>0.003</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4107</v>
+        <v>2.2588</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.0261</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4339</v>
+        <v>-0.9727</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2108</v>
+        <v>0.9988</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.1704</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.9384</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. ADEBAYO</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5507</v>
+        <v>-0.7191</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9737</v>
+        <v>-0.9227</v>
       </c>
       <c r="F16" t="n">
-        <v>0.423</v>
+        <v>0.2036</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.5525</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3046</v>
+        <v>0.3763</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3917</v>
+        <v>-0.9288</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0167</v>
+        <v>-0.016</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4114</v>
+        <v>0.6813</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3947</v>
+        <v>-0.6974</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1037</v>
+        <v>-0.5365</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1068</v>
+        <v>-0.305</v>
       </c>
       <c r="O16" t="n">
-        <v>0.003</v>
+        <v>-0.2314</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2588</v>
+        <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4986</v>
+        <v>0.4494</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.7049</v>
+        <v>0.1201</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2063</v>
+        <v>0.3294</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1704</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-1.0473</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4217</v>
+        <v>-1.6464</v>
       </c>
       <c r="F17" t="n">
-        <v>0.664</v>
+        <v>0.5991</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4991</v>
+        <v>-1.4715</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.7573</v>
+        <v>-1.3558</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2582</v>
+        <v>-0.1157</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0375</v>
+        <v>-1.3558</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0375</v>
+        <v>-1.3558</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4616</v>
+        <v>-0.1157</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7198</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2582</v>
+        <v>-0.1157</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9468</v>
+        <v>-0.1918</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7165</v>
+        <v>-0.2906</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2303</v>
+        <v>0.0988</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1314</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2112</v>
+        <v>-1.5805</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.751</v>
+        <v>-2.3631</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.7826</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4715</v>
+        <v>-2.4991</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3558</v>
+        <v>-2.7573</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1157</v>
+        <v>0.2582</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3558</v>
+        <v>-1.0375</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3558</v>
+        <v>-1.0375</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1157</v>
+        <v>-1.4616</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.7198</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1157</v>
+        <v>0.2582</v>
       </c>
       <c r="P18" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3557</v>
+        <v>0.1239</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3952</v>
+        <v>-0.225</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0395</v>
+        <v>0.3489</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1314</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5857</v>
+        <v>-3.3033</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6193</v>
+        <v>-1.5147</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9664</v>
+        <v>-1.7886</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0026</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6796</v>
+        <v>-0.3972</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3566</v>
+        <v>-0.252</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.323</v>
+        <v>-0.1452</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5195</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.2014</v>
+        <v>-3.5895</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8732</v>
+        <v>-4.3502</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6718</v>
+        <v>0.7607</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9438</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6149</v>
+        <v>-0.0029</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.651</v>
+        <v>-0.128</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0361</v>
+        <v>0.125</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.547</v>
+        <v>-4.9647</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0901</v>
+        <v>-4.5671</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4569</v>
+        <v>-0.3976</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8159</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.0524</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9145</v>
+        <v>-0.3915</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2798</v>
+        <v>0.3391</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0698</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.4249</v>
+        <v>-11.4251</v>
       </c>
       <c r="E22" t="n">
         <v>-15.9265</v>
       </c>
       <c r="F22" t="n">
-        <v>4.501500000000001</v>
+        <v>4.501499999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-19.1159</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.0923</v>
+        <v>-8.092300000000002</v>
       </c>
       <c r="I22" t="n">
         <v>-11.0238</v>
@@ -2170,16 +2170,16 @@
         <v>14.3741</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1428</v>
+        <v>1.1426</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.8685</v>
+        <v>-2.8686</v>
       </c>
       <c r="U22" t="n">
         <v>4.0111</v>
       </c>
       <c r="V22" t="n">
-        <v>5.521500000000001</v>
+        <v>5.5215</v>
       </c>
       <c r="W22" t="n">
         <v>9.5604</v>
